--- a/healthcare_surveys/023_ai_literacy_in_healthcare_evaluation_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/023_ai_literacy_in_healthcare_evaluation_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -963,12 +963,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'physician_/_specialist',_'value':_'physician'}</t>
+          <t>physician_/_specialist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Physician / Specialist', 'value': 'physician'}</t>
+          <t>Physician / Specialist</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'registered_nurse_/_practitioner',_'value':_'nurse'}</t>
+          <t>registered_nurse_/_practitioner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Registered Nurse / Practitioner', 'value': 'nurse'}</t>
+          <t>Registered Nurse / Practitioner</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'medical_technician_/_radiographer',_'value':_'technician'}</t>
+          <t>medical_technician_/_radiographer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Medical Technician / Radiographer', 'value': 'technician'}</t>
+          <t>Medical Technician / Radiographer</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_administrator_/_management',_'value':_'admin'}</t>
+          <t>healthcare_administrator_/_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare Administrator / Management', 'value': 'admin'}</t>
+          <t>Healthcare Administrator / Management</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'researcher_/_academic',_'value':_'researcher'}</t>
+          <t>researcher_/_academic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Researcher / Academic', 'value': 'researcher'}</t>
+          <t>Researcher / Academic</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'pharmacist',_'value':_'pharmacist'}</t>
+          <t>pharmacist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Pharmacist', 'value': 'pharmacist'}</t>
+          <t>Pharmacist</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_familiar_at_all',_'value':_'none'}</t>
+          <t>not_familiar_at_all</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not familiar at all', 'value': 'none'}</t>
+          <t>Not familiar at all</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_familiar_(heard_terms)',_'value':_'low'}</t>
+          <t>slightly_familiar_(heard_terms)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly familiar (Heard terms)', 'value': 'low'}</t>
+          <t>Slightly familiar (Heard terms)</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'moderately_familiar_(understand_basic_concepts)',_'value':_'moderate'}</t>
+          <t>moderately_familiar_(understand_basic_concepts)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately familiar (Understand basic concepts)', 'value': 'moderate'}</t>
+          <t>Moderately familiar (Understand basic concepts)</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_familiar_(can_explain_to_others)',_'value':_'high'}</t>
+          <t>very_familiar_(can_explain_to_others)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very familiar (Can explain to others)', 'value': 'high'}</t>
+          <t>Very familiar (Can explain to others)</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_(few_times_a_year)',_'value':_'rarely'}</t>
+          <t>rarely_(few_times_a_year)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely (Few times a year)', 'value': 'rarely'}</t>
+          <t>Rarely (Few times a year)</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally_(monthly)',_'value':_'occasionally'}</t>
+          <t>occasionally_(monthly)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally (Monthly)', 'value': 'occasionally'}</t>
+          <t>Occasionally (Monthly)</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'frequently_(weekly)',_'value':_'frequently'}</t>
+          <t>frequently_(weekly)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently (Weekly)', 'value': 'frequently'}</t>
+          <t>Frequently (Weekly)</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 'daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'ai-assisted_diagnostic_imaging_(e.g.,_x-ray/mri_analysis)',_'value':_'imaging'}</t>
+          <t>ai-assisted_diagnostic_imaging_(e.g.,_x-ray/mri_analysis)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'AI-assisted Diagnostic Imaging (e.g., X-ray/MRI analysis)', 'value': 'imaging'}</t>
+          <t>AI-assisted Diagnostic Imaging (e.g., X-ray/MRI analysis)</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'predictive_risk_analytics_(e.g.,_sepsis_prediction)',_'value':_'predictive_risk'}</t>
+          <t>predictive_risk_analytics_(e.g.,_sepsis_prediction)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Predictive Risk Analytics (e.g., Sepsis prediction)', 'value': 'predictive_risk'}</t>
+          <t>Predictive Risk Analytics (e.g., Sepsis prediction)</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'clinical_decision_support_systems_(cdss)',_'value':_'cdss'}</t>
+          <t>clinical_decision_support_systems_(cdss)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Clinical Decision Support Systems (CDSS)', 'value': 'cdss'}</t>
+          <t>Clinical Decision Support Systems (CDSS)</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'ai_virtual_assistants_/_chatbots_for_patients',_'value':_'patient_chatbots'}</t>
+          <t>ai_virtual_assistants_/_chatbots_for_patients</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'AI Virtual Assistants / Chatbots for Patients', 'value': 'patient_chatbots'}</t>
+          <t>AI Virtual Assistants / Chatbots for Patients</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'automated_transcription_/_scribes',_'value':_'scribes'}</t>
+          <t>automated_transcription_/_scribes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Automated Transcription / Scribes', 'value': 'scribes'}</t>
+          <t>Automated Transcription / Scribes</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'robotic_surgery_assistance',_'value':_'robotic_surgery'}</t>
+          <t>robotic_surgery_assistance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Robotic Surgery Assistance', 'value': 'robotic_surgery'}</t>
+          <t>Robotic Surgery Assistance</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'increased_diagnostic_accuracy',_'value':_'accuracy'}</t>
+          <t>increased_diagnostic_accuracy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Increased Diagnostic Accuracy', 'value': 'accuracy'}</t>
+          <t>Increased Diagnostic Accuracy</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'reduced_administrative_burden',_'value':_'reduced_admin'}</t>
+          <t>reduced_administrative_burden</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Reduced Administrative Burden', 'value': 'reduced_admin'}</t>
+          <t>Reduced Administrative Burden</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'early_detection_of_diseases',_'value':_'early_detection'}</t>
+          <t>early_detection_of_diseases</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Early Detection of Diseases', 'value': 'early_detection'}</t>
+          <t>Early Detection of Diseases</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'personalized_treatment_plans',_'value':_'personalization'}</t>
+          <t>personalized_treatment_plans</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Personalized Treatment Plans', 'value': 'personalization'}</t>
+          <t>Personalized Treatment Plans</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'faster_processing_of_lab_results',_'value':_'speed'}</t>
+          <t>faster_processing_of_lab_results</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Faster Processing of Lab Results', 'value': 'speed'}</t>
+          <t>Faster Processing of Lab Results</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'patient_data_privacy_&amp;_security',_'value':_'privacy'}</t>
+          <t>patient_data_privacy_&amp;_security</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Patient Data Privacy &amp; Security', 'value': 'privacy'}</t>
+          <t>Patient Data Privacy &amp; Security</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'algorithmic_bias_&amp;_inequality',_'value':_'bias'}</t>
+          <t>algorithmic_bias_&amp;_inequality</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Algorithmic Bias &amp; Inequality', 'value': 'bias'}</t>
+          <t>Algorithmic Bias &amp; Inequality</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'liability_&amp;_accountability_for_errors',_'value':_'liability'}</t>
+          <t>liability_&amp;_accountability_for_errors</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Liability &amp; Accountability for Errors', 'value': 'liability'}</t>
+          <t>Liability &amp; Accountability for Errors</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_"loss_of_the_'human_touch'_in_care",_'value':_'human_touch'}</t>
+          <t>loss_of_the_'human_touch'_in_care</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': "Loss of the 'Human Touch' in care", 'value': 'human_touch'}</t>
+          <t>Loss of the 'Human Touch' in care</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'over-reliance_on_technology',_'value':_'overreliance'}</t>
+          <t>over-reliance_on_technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Over-reliance on Technology', 'value': 'overreliance'}</t>
+          <t>Over-reliance on Technology</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_definitely',_'value':_true}</t>
+          <t>yes,_definitely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, definitely', 'value': True}</t>
+          <t>Yes, definitely</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_if_provided_during_work_hours',_'value':_'yes_conditional'}</t>
+          <t>yes,_if_provided_during_work_hours</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, if provided during work hours', 'value': 'yes_conditional'}</t>
+          <t>Yes, if provided during work hours</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'maybe_(need_more_information)',_'value':_'maybe'}</t>
+          <t>maybe_(need_more_information)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe (Need more information)', 'value': 'maybe'}</t>
+          <t>Maybe (Need more information)</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree',_'value':_1}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree', 'value': 1}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'disagree',_'value':_2}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree', 'value': 2}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'agree',_'value':_4}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Agree', 'value': 4}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree',_'value':_5}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree', 'value': 5}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
